--- a/04_lms_courses.xlsx
+++ b/04_lms_courses.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>course_id</t>
   </si>
@@ -28,7 +28,7 @@
     <t>duration_hours</t>
   </si>
   <si>
-    <t>price</t>
+    <t>description</t>
   </si>
   <si>
     <t>C001</t>
@@ -43,6 +43,9 @@
     <t>beginner</t>
   </si>
   <si>
+    <t>Базовый курс по работе с Excel</t>
+  </si>
+  <si>
     <t>C002</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t>intermediate</t>
   </si>
   <si>
+    <t>Методологии и инструменты</t>
+  </si>
+  <si>
     <t>C003</t>
   </si>
   <si>
@@ -67,6 +73,9 @@
     <t>advanced</t>
   </si>
   <si>
+    <t>Развитие лидерских качеств</t>
+  </si>
+  <si>
     <t>C004</t>
   </si>
   <si>
@@ -76,12 +85,18 @@
     <t>Data Science</t>
   </si>
   <si>
+    <t>Введение в аналитику</t>
+  </si>
+  <si>
     <t>C005</t>
   </si>
   <si>
     <t>Переговоры</t>
   </si>
   <si>
+    <t>Техники ведения переговоров</t>
+  </si>
+  <si>
     <t>C006</t>
   </si>
   <si>
@@ -91,12 +106,18 @@
     <t>Finance</t>
   </si>
   <si>
+    <t>Основы финансовой грамотности</t>
+  </si>
+  <si>
     <t>C007</t>
   </si>
   <si>
     <t>Продуктовая аналитика</t>
   </si>
   <si>
+    <t>Продвинутая аналитика</t>
+  </si>
+  <si>
     <t>C008</t>
   </si>
   <si>
@@ -104,6 +125,9 @@
   </si>
   <si>
     <t>Programming</t>
+  </si>
+  <si>
+    <t>Основы программирования</t>
   </si>
 </sst>
 </file>
@@ -369,8 +393,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="28.38"/>
-    <col customWidth="1" min="5" max="5" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="34.25"/>
+    <col customWidth="1" min="3" max="3" width="13.0"/>
+    <col customWidth="1" min="5" max="5" width="18.38"/>
+    <col customWidth="1" min="6" max="6" width="32.38"/>
+    <col customWidth="1" min="8" max="8" width="51.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -392,6 +419,8 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -406,152 +435,216 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>150000.0</v>
-      </c>
+      <c r="E2" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2">
-        <v>72.0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>250000.0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>20000.0</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2">
-        <v>144.0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>350000.0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E5" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>180000.0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E6" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>220000.0</v>
-      </c>
+      <c r="E7" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2">
-        <v>144.0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>300000.0</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E8" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="2">
-        <v>72.0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>280000.0</v>
-      </c>
+      <c r="E9" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
